--- a/data/trans_dic/P22$concerIndv-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerIndv-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado individualmente</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado individualmente (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 12,61</t>
+          <t>7,15; 12,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,09; 13,51</t>
+          <t>7,08; 13,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 12,92</t>
+          <t>7,02; 12,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,2; 18,38</t>
+          <t>12,18; 18,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 15,26</t>
+          <t>7,79; 15,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 11,41</t>
+          <t>5,39; 11,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,37; 18,02</t>
+          <t>10,13; 17,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,79; 22,82</t>
+          <t>16,83; 22,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 12,43</t>
+          <t>8,04; 12,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,77; 11,74</t>
+          <t>7,06; 11,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,19; 13,96</t>
+          <t>9,23; 14,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,95; 19,25</t>
+          <t>15,21; 19,43</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,79</t>
+          <t>2,26; 6,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 9,55</t>
+          <t>4,02; 9,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 10,01</t>
+          <t>4,59; 10,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 17,2</t>
+          <t>9,42; 17,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,8</t>
+          <t>3,59; 8,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 9,44</t>
+          <t>3,26; 9,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,13; 14,55</t>
+          <t>8,1; 14,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,61; 21,15</t>
+          <t>14,03; 20,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 6,69</t>
+          <t>3,53; 6,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,52; 8,56</t>
+          <t>4,49; 8,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 11,18</t>
+          <t>6,87; 11,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,33; 17,25</t>
+          <t>12,62; 17,2</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,59</t>
+          <t>1,28; 4,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,23</t>
+          <t>1,32; 4,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,85</t>
+          <t>0,99; 3,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,98</t>
+          <t>0,82; 5,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,75</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,72</t>
+          <t>0,8; 5,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,51</t>
+          <t>2,27; 8,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 12,77</t>
+          <t>5,65; 12,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,77</t>
+          <t>1,1; 3,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,87</t>
+          <t>1,47; 3,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,42</t>
+          <t>1,53; 4,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,17</t>
+          <t>1,72; 6,24</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,68</t>
+          <t>0,56; 1,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,5</t>
+          <t>0,83; 2,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,19</t>
+          <t>0,69; 2,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,3</t>
+          <t>2,71; 5,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,17</t>
+          <t>1,81; 4,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,18</t>
+          <t>2,33; 5,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,25</t>
+          <t>1,23; 3,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,46</t>
+          <t>2,66; 7,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,26</t>
+          <t>1,16; 2,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,11</t>
+          <t>1,72; 3,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,29</t>
+          <t>1,15; 2,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,71</t>
+          <t>3,14; 5,66</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,3</t>
+          <t>0,38; 2,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,92</t>
+          <t>0,32; 1,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,37</t>
+          <t>0,34; 2,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,52</t>
+          <t>0,5; 2,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,53</t>
+          <t>0,78; 2,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,98</t>
+          <t>0,78; 2,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,08</t>
+          <t>1,84; 4,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,64</t>
+          <t>0,38; 1,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,11</t>
+          <t>0,84; 2,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,96</t>
+          <t>0,75; 2,04</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,0</t>
+          <t>1,45; 2,91</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,14</t>
+          <t>0,56; 3,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,56</t>
+          <t>0,35; 2,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,92</t>
+          <t>2,77; 8,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,28</t>
+          <t>0,0; 7,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,23</t>
+          <t>2,85; 5,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,01</t>
+          <t>1,79; 3,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,32</t>
+          <t>1,95; 4,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,81</t>
+          <t>2,26; 4,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,5</t>
+          <t>2,65; 4,58</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,47</t>
+          <t>1,63; 3,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,57</t>
+          <t>2,44; 4,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,58</t>
+          <t>1,99; 4,63</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,42</t>
+          <t>2,25; 3,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,03</t>
+          <t>2,69; 4,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,02</t>
+          <t>2,75; 4,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,96</t>
+          <t>4,74; 7,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,7</t>
+          <t>3,32; 4,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,04</t>
+          <t>2,72; 4,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,25</t>
+          <t>3,73; 5,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,23; 8,58</t>
+          <t>6,12; 8,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,86</t>
+          <t>2,95; 3,85</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 3,82</t>
+          <t>2,83; 3,77</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,52</t>
+          <t>3,43; 4,37</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,81; 7,54</t>
+          <t>5,77; 7,51</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado individualmente</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado individualmente (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>33968; 59568</t>
+          <t>33757; 59522</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30984; 59086</t>
+          <t>30961; 58571</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29617; 55421</t>
+          <t>30116; 54575</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61644; 92851</t>
+          <t>61532; 93841</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23390; 46806</t>
+          <t>23889; 46384</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16432; 35895</t>
+          <t>16942; 35725</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36005; 62523</t>
+          <t>35164; 62272</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>75117; 102095</t>
+          <t>75295; 101672</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63061; 96838</t>
+          <t>62611; 97233</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50893; 88244</t>
+          <t>53101; 85200</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71340; 108372</t>
+          <t>71661; 110210</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>142447; 183433</t>
+          <t>144882; 185063</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8032; 24920</t>
+          <t>8296; 23148</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17416; 39985</t>
+          <t>16838; 39229</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16135; 37674</t>
+          <t>17286; 38351</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42244; 77776</t>
+          <t>42608; 78609</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13882; 32716</t>
+          <t>13367; 32369</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11113; 31919</t>
+          <t>11013; 30655</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30250; 54165</t>
+          <t>30146; 54825</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>55904; 80918</t>
+          <t>53671; 79093</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25784; 49444</t>
+          <t>26047; 49326</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34181; 64807</t>
+          <t>33958; 62388</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51158; 83666</t>
+          <t>51432; 84643</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>102933; 144015</t>
+          <t>105386; 143619</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6576; 24874</t>
+          <t>6953; 23521</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9224; 26640</t>
+          <t>8310; 26592</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5218; 20076</t>
+          <t>5165; 19795</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6252; 33300</t>
+          <t>5475; 35183</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6291</t>
+          <t>0; 6765</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2058; 14876</t>
+          <t>2093; 15241</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3810; 14137</t>
+          <t>3779; 14033</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9793; 21322</t>
+          <t>9435; 20584</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7514; 26745</t>
+          <t>7777; 25678</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13249; 34388</t>
+          <t>13074; 35454</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12406; 30427</t>
+          <t>10552; 27847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12732; 51497</t>
+          <t>14367; 52109</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7089; 20798</t>
+          <t>6968; 20127</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9624; 28893</t>
+          <t>9653; 27957</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8757; 25133</t>
+          <t>7982; 24171</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28989; 54885</t>
+          <t>28036; 54282</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12584; 29776</t>
+          <t>12918; 30531</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18055; 39746</t>
+          <t>17866; 40881</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9896; 26737</t>
+          <t>10129; 28108</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26163; 72989</t>
+          <t>26018; 72752</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22638; 43991</t>
+          <t>22540; 44500</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32081; 59807</t>
+          <t>33054; 60000</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21634; 45082</t>
+          <t>22765; 46256</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>66003; 114981</t>
+          <t>63257; 113860</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3953</t>
+          <t>0; 5204</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1944; 11729</t>
+          <t>1924; 11662</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1988; 11891</t>
+          <t>2008; 11164</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1537; 11248</t>
+          <t>1620; 11501</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3259; 14359</t>
+          <t>2848; 13983</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6031; 19239</t>
+          <t>5925; 17853</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5799; 21974</t>
+          <t>5734; 20984</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15981; 34225</t>
+          <t>15461; 34485</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3141; 15067</t>
+          <t>3535; 16030</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10514; 26781</t>
+          <t>10693; 25835</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9522; 26534</t>
+          <t>10231; 27712</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19219; 39397</t>
+          <t>19116; 38248</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1672; 9341</t>
+          <t>1677; 9370</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>947; 6832</t>
+          <t>942; 7736</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7960; 22745</t>
+          <t>7954; 23003</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 19903</t>
+          <t>0; 18020</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36759; 65178</t>
+          <t>35493; 63233</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20021; 44508</t>
+          <t>19826; 42525</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22147; 46682</t>
+          <t>21086; 45894</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17322; 36601</t>
+          <t>17213; 37204</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41482; 69488</t>
+          <t>40930; 70640</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23124; 47809</t>
+          <t>22382; 46969</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33191; 62556</t>
+          <t>33410; 62250</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19889; 45875</t>
+          <t>19975; 46387</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>73145; 111734</t>
+          <t>73487; 110095</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>92262; 137803</t>
+          <t>92095; 136988</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>91359; 135989</t>
+          <t>92870; 135214</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>155972; 234935</t>
+          <t>160034; 236676</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>109676; 158713</t>
+          <t>112188; 157559</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>98861; 143399</t>
+          <t>96485; 144201</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>135139; 184971</t>
+          <t>131450; 183322</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>222631; 306754</t>
+          <t>218713; 306958</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>197854; 256411</t>
+          <t>195589; 255508</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>204643; 266639</t>
+          <t>197356; 262836</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>241577; 312413</t>
+          <t>237257; 302187</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>403863; 523968</t>
+          <t>401177; 522039</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$concerIndv-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerIndv-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,15; 12,6</t>
+          <t>7,25; 12,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,08; 13,4</t>
+          <t>7,24; 13,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,02; 12,72</t>
+          <t>7,02; 12,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,18; 18,57</t>
+          <t>12,93; 18,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,79; 15,12</t>
+          <t>7,65; 14,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 11,36</t>
+          <t>5,29; 11,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 17,94</t>
+          <t>10,01; 17,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,83; 22,72</t>
+          <t>16,56; 22,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 12,48</t>
+          <t>8,07; 12,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 11,33</t>
+          <t>7,06; 11,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,23; 14,2</t>
+          <t>9,28; 14,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,21; 19,43</t>
+          <t>15,44; 19,64</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,31</t>
+          <t>2,39; 6,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,02; 9,37</t>
+          <t>4,19; 9,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 10,19</t>
+          <t>4,14; 9,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,42; 17,38</t>
+          <t>9,33; 15,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 8,7</t>
+          <t>3,51; 8,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 9,07</t>
+          <t>3,39; 9,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,1; 14,73</t>
+          <t>8,07; 14,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,03; 20,67</t>
+          <t>14,5; 20,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,68</t>
+          <t>3,46; 6,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 8,24</t>
+          <t>4,48; 8,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,31</t>
+          <t>6,93; 11,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,62; 17,2</t>
+          <t>12,62; 17,34</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,34</t>
+          <t>1,13; 4,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,22</t>
+          <t>1,36; 4,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,79</t>
+          <t>1,07; 3,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,26</t>
+          <t>3,23; 7,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 3,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,86</t>
+          <t>0,79; 5,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 8,45</t>
+          <t>2,24; 8,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 12,33</t>
+          <t>6,01; 12,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,62</t>
+          <t>1,05; 3,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,99</t>
+          <t>1,48; 3,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,05</t>
+          <t>1,61; 4,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,24</t>
+          <t>4,65; 8,43</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,63</t>
+          <t>0,57; 1,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,41</t>
+          <t>0,87; 2,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,1</t>
+          <t>0,69; 2,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,25</t>
+          <t>2,82; 5,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,27</t>
+          <t>1,67; 4,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,33</t>
+          <t>2,41; 5,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,42</t>
+          <t>1,17; 3,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,44</t>
+          <t>5,3; 8,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,28</t>
+          <t>1,14; 2,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,12</t>
+          <t>1,62; 3,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,35</t>
+          <t>1,16; 2,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,66</t>
+          <t>4,32; 6,33</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,28</t>
+          <t>0,38; 2,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,8</t>
+          <t>0,32; 1,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,42</t>
+          <t>0,52; 3,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,46</t>
+          <t>0,54; 2,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,34</t>
+          <t>0,77; 2,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,85</t>
+          <t>0,74; 2,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,11</t>
+          <t>2,07; 4,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,74</t>
+          <t>0,4; 1,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,03</t>
+          <t>0,77; 2,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,04</t>
+          <t>0,69; 1,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,91</t>
+          <t>1,62; 3,12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,15</t>
+          <t>0,56; 3,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,9</t>
+          <t>0,35; 2,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 8,01</t>
+          <t>2,62; 7,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,49</t>
+          <t>0,0; 6,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,07</t>
+          <t>2,99; 5,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,83</t>
+          <t>1,83; 3,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,25</t>
+          <t>2,05; 4,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,89</t>
+          <t>2,33; 5,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,58</t>
+          <t>2,59; 4,47</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,41</t>
+          <t>1,6; 3,42</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,55</t>
+          <t>2,53; 4,72</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,63</t>
+          <t>2,09; 4,57</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,37</t>
+          <t>2,28; 3,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,0</t>
+          <t>2,67; 4,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,0</t>
+          <t>2,69; 3,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,01</t>
+          <t>5,67; 7,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,32; 4,67</t>
+          <t>3,36; 4,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,06</t>
+          <t>2,75; 4,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 5,2</t>
+          <t>3,75; 5,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,12; 8,59</t>
+          <t>7,44; 9,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,95; 3,85</t>
+          <t>2,97; 3,84</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 3,77</t>
+          <t>2,89; 3,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 4,37</t>
+          <t>3,47; 4,36</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,77; 7,51</t>
+          <t>6,86; 8,11</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76353</t>
+          <t>85231</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88083</t>
+          <t>96764</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>164437</t>
+          <t>181995</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>33757; 59522</t>
+          <t>34256; 60025</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30961; 58571</t>
+          <t>31634; 60674</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30116; 54575</t>
+          <t>30136; 54887</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61532; 93841</t>
+          <t>71212; 104326</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23889; 46384</t>
+          <t>23451; 45648</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16942; 35725</t>
+          <t>16646; 36352</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35164; 62272</t>
+          <t>34738; 61970</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>75295; 101672</t>
+          <t>80857; 110361</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62611; 97233</t>
+          <t>62888; 96340</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53101; 85200</t>
+          <t>53063; 87123</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71661; 110210</t>
+          <t>71995; 108905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>144882; 185063</t>
+          <t>160423; 204023</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56941</t>
+          <t>59996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>66175</t>
+          <t>73815</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>123115</t>
+          <t>133811</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8296; 23148</t>
+          <t>8780; 24385</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16838; 39229</t>
+          <t>17559; 40016</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17286; 38351</t>
+          <t>15562; 36696</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42608; 78609</t>
+          <t>45076; 76806</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13367; 32369</t>
+          <t>13053; 31863</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11013; 30655</t>
+          <t>11455; 30851</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30146; 54825</t>
+          <t>30041; 54386</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53671; 79093</t>
+          <t>61372; 87707</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26047; 49326</t>
+          <t>25579; 50435</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33958; 62388</t>
+          <t>33906; 63327</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51432; 84643</t>
+          <t>51893; 84458</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>105386; 143619</t>
+          <t>114385; 157136</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18667</t>
+          <t>24039</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>16939</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33015</t>
+          <t>40979</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6953; 23521</t>
+          <t>6126; 24692</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8310; 26592</t>
+          <t>8540; 26101</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5165; 19795</t>
+          <t>5559; 20200</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5475; 35183</t>
+          <t>15256; 36643</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6765</t>
+          <t>0; 6163</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2093; 15241</t>
+          <t>2061; 14165</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3779; 14033</t>
+          <t>3727; 14521</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9435; 20584</t>
+          <t>11262; 23660</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7777; 25678</t>
+          <t>7473; 25253</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13074; 35454</t>
+          <t>13197; 33738</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10552; 27847</t>
+          <t>11068; 29082</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14367; 52109</t>
+          <t>30663; 55541</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40434</t>
+          <t>44270</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>52066</t>
+          <t>59845</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92500</t>
+          <t>104115</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6968; 20127</t>
+          <t>7003; 19493</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9653; 27957</t>
+          <t>10036; 28085</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7982; 24171</t>
+          <t>7907; 24009</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28036; 54282</t>
+          <t>31902; 59255</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12918; 30531</t>
+          <t>11928; 29963</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17866; 40881</t>
+          <t>18449; 38948</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10129; 28108</t>
+          <t>9646; 27299</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26018; 72752</t>
+          <t>45665; 74158</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22540; 44500</t>
+          <t>22264; 44165</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33054; 60000</t>
+          <t>31194; 59430</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22765; 46256</t>
+          <t>22868; 45105</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>63257; 113860</t>
+          <t>86003; 126171</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23748</t>
+          <t>24707</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28327</t>
+          <t>32235</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5204</t>
+          <t>0; 3907</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1924; 11662</t>
+          <t>1921; 11722</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2008; 11164</t>
+          <t>1975; 11193</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1620; 11501</t>
+          <t>2972; 17411</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2848; 13983</t>
+          <t>3061; 14804</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5925; 17853</t>
+          <t>5871; 18942</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5734; 20984</t>
+          <t>5485; 21163</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15461; 34485</t>
+          <t>17200; 34092</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3535; 16030</t>
+          <t>3683; 15420</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10693; 25835</t>
+          <t>9831; 26915</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10231; 27712</t>
+          <t>9354; 26666</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19116; 38248</t>
+          <t>22669; 43635</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>25376</t>
+          <t>29479</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>29281</t>
+          <t>32979</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1677; 9370</t>
+          <t>1669; 9307</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>942; 7736</t>
+          <t>938; 7772</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7954; 23003</t>
+          <t>7522; 22714</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 18020</t>
+          <t>0; 15709</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35493; 63233</t>
+          <t>37237; 63843</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19826; 42525</t>
+          <t>20259; 44142</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21086; 45894</t>
+          <t>22156; 46249</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17213; 37204</t>
+          <t>19688; 42755</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40930; 70640</t>
+          <t>39925; 68960</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22382; 46969</t>
+          <t>21993; 47060</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33410; 62250</t>
+          <t>34615; 64587</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19975; 46387</t>
+          <t>22566; 49440</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200879</t>
+          <t>224564</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>269795</t>
+          <t>301550</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>470674</t>
+          <t>526114</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>73487; 110095</t>
+          <t>74448; 111552</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>92095; 136988</t>
+          <t>91444; 137463</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>92870; 135214</t>
+          <t>91065; 133855</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>160034; 236676</t>
+          <t>195353; 257962</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>112188; 157559</t>
+          <t>113559; 158476</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>96485; 144201</t>
+          <t>97661; 143170</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>131450; 183322</t>
+          <t>132083; 183909</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>218713; 306958</t>
+          <t>270266; 332145</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>195589; 255508</t>
+          <t>197026; 255238</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>197356; 262836</t>
+          <t>201303; 264907</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>237257; 302187</t>
+          <t>239745; 301258</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>401177; 522039</t>
+          <t>485174; 573812</t>
         </is>
       </c>
     </row>
